--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{158B95FF-CE21-45B3-B2BF-F3200F980F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEB74888-2858-4E8A-87F6-56D10E23DC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2304,7 +2304,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{151C8DD5-1DE4-49BE-A198-91834FDB6EFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C177E2-577F-400B-AB6D-C4572CCA1916}">
   <dimension ref="B2:AF256"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -7267,7 +7267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E95A4E-2128-4D4E-9D18-CC370FF3AFCD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43221EF-6FC6-472D-B8B6-F1286671D95B}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -20970,7 +20970,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D445B2-4C42-49A3-A080-CF10DFC5C5C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61E43AD4-3490-4ACA-B344-C85F2CC9B670}">
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
